--- a/data/trans_orig/AIRE_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan la contaminación ambiental en su municipio o lugar de residencia en 2023</t>
+          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan la contaminación ambiental en su municipio o lugar de residencia en 2023 (tasa de respuesta: 99,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,49 +745,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>23610</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>17394</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31206</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>9,26%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>23610</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17498</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>31138</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45619</t>
+          <t>46882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72878</t>
+          <t>74057</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98913</t>
+          <t>100304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136647</t>
+          <t>137966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163895</t>
+          <t>164224</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>217091</t>
+          <t>218447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255389</t>
+          <t>257881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46208</t>
+          <t>46165</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67372</t>
+          <t>68062</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52267</t>
+          <t>52153</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73922</t>
+          <t>73240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>104743</t>
+          <t>103703</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>135419</t>
+          <t>134451</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>21791</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40659</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42498</t>
+          <t>40751</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61886</t>
+          <t>62060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67975</t>
+          <t>69252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95608</t>
+          <t>98283</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25417</t>
+          <t>24899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44335</t>
+          <t>44194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40108</t>
+          <t>40596</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59363</t>
+          <t>60431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>69056</t>
+          <t>70325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96772</t>
+          <t>96994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61975</t>
+          <t>61499</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122547</t>
+          <t>122612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30377</t>
+          <t>29640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86254</t>
+          <t>86603</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96926</t>
+          <t>98325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188885</t>
+          <t>192682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160374</t>
+          <t>162025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>217027</t>
+          <t>219335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>259516</t>
+          <t>260464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>663866</t>
+          <t>657088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>438842</t>
+          <t>434089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>967794</t>
+          <t>966153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>283212</t>
+          <t>285741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>344866</t>
+          <t>346635</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120293</t>
+          <t>129430</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335295</t>
+          <t>335688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372102</t>
+          <t>397587</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>660513</t>
+          <t>663581</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106749</t>
+          <t>106580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149425</t>
+          <t>149670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47737</t>
+          <t>48744</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136264</t>
+          <t>135429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150167</t>
+          <t>154526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>270963</t>
+          <t>272693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63924</t>
+          <t>61871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96946</t>
+          <t>95995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41843</t>
+          <t>43060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118757</t>
+          <t>118867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>105780</t>
+          <t>106727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196245</t>
+          <t>196174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29758</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29251</t>
+          <t>28248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27668</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51081</t>
+          <t>52517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21895</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15866</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30708</t>
+          <t>31510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25948</t>
+          <t>25140</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47729</t>
+          <t>47021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89281</t>
+          <t>88562</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120297</t>
+          <t>123226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92287</t>
+          <t>92118</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>118695</t>
+          <t>117637</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>188224</t>
+          <t>186675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>230802</t>
+          <t>228814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24165</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46554</t>
+          <t>44129</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>25167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44015</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>54039</t>
+          <t>53649</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82389</t>
+          <t>82470</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16402</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36549</t>
+          <t>36012</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24660</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42849</t>
+          <t>43442</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46831</t>
+          <t>47260</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72718</t>
+          <t>74777</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91014</t>
+          <t>91612</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153137</t>
+          <t>157423</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>63444</t>
+          <t>65028</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129805</t>
+          <t>130187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>167538</t>
+          <t>169598</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>268755</t>
+          <t>267427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>256313</t>
+          <t>255286</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>320718</t>
+          <t>319838</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>434984</t>
+          <t>435368</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>990502</t>
+          <t>913998</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>707133</t>
+          <t>711043</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1330095</t>
+          <t>1341388</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,11%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>438537</t>
+          <t>440040</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>511265</t>
+          <t>514421</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>224042</t>
+          <t>262760</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>499013</t>
+          <t>500669</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>682589</t>
+          <t>650220</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>986529</t>
+          <t>985972</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>166454</t>
+          <t>166118</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>220505</t>
+          <t>217463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114407</t>
+          <t>115357</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>224409</t>
+          <t>223450</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>277767</t>
+          <t>289206</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>420929</t>
+          <t>422857</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117176</t>
+          <t>116576</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>157039</t>
+          <t>160290</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92306</t>
+          <t>102225</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>201967</t>
+          <t>205035</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>226487</t>
+          <t>236532</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>347974</t>
+          <t>346208</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12309</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>20710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17394</t>
+          <t>18497</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>33564</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35919</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27375</t>
+          <t>28367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46882</t>
+          <t>47716</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86084</t>
+          <t>103592</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74057</t>
+          <t>91154</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100304</t>
+          <t>122702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>164066</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137966</t>
+          <t>148391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164224</t>
+          <t>178929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>236690</t>
+          <t>267659</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>218447</t>
+          <t>247529</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>257881</t>
+          <t>287929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,42%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55923</t>
+          <t>63024</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46165</t>
+          <t>50206</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68062</t>
+          <t>75309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62820</t>
+          <t>68962</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>52153</t>
+          <t>58186</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>73240</t>
+          <t>80668</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118743</t>
+          <t>131986</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103703</t>
+          <t>115337</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>134451</t>
+          <t>149914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30156</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21791</t>
+          <t>24711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>46204</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51152</t>
+          <t>58153</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62060</t>
+          <t>70532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>81308</t>
+          <t>91973</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69252</t>
+          <t>78140</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98283</t>
+          <t>107453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33827</t>
+          <t>36929</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>27858</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44194</t>
+          <t>47418</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>48658</t>
+          <t>53927</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40596</t>
+          <t>43626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60431</t>
+          <t>64901</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>82485</t>
+          <t>90855</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>70325</t>
+          <t>77129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96994</t>
+          <t>105615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>218299</t>
+          <t>250424</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>218299</t>
+          <t>250424</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>218299</t>
+          <t>250424</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>336846</t>
+          <t>369909</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>336846</t>
+          <t>369909</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>336846</t>
+          <t>369909</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>555145</t>
+          <t>620333</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>555145</t>
+          <t>620333</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>555145</t>
+          <t>620333</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87772</t>
+          <t>81085</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61499</t>
+          <t>59855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122612</t>
+          <t>110803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61752</t>
+          <t>70839</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29640</t>
+          <t>56428</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86603</t>
+          <t>90251</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>149524</t>
+          <t>151924</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98325</t>
+          <t>123500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192682</t>
+          <t>188499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>186999</t>
+          <t>218904</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>162025</t>
+          <t>193156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>219335</t>
+          <t>251597</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>414437</t>
+          <t>241493</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260464</t>
+          <t>217529</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657088</t>
+          <t>266483</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>601436</t>
+          <t>460397</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>434089</t>
+          <t>420543</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>966153</t>
+          <t>497576</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315119</t>
+          <t>336504</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285741</t>
+          <t>305942</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>346635</t>
+          <t>369333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,67 +1668,67 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>253957</t>
+          <t>271551</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>129430</t>
+          <t>249751</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335688</t>
+          <t>297695</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>608055</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>568404</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>647729</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
           <t>36,59%</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>569076</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>397587</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>663581</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>33,22%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>128033</t>
+          <t>142823</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106580</t>
+          <t>119752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149670</t>
+          <t>167057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>100594</t>
+          <t>111292</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48744</t>
+          <t>95699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>135429</t>
+          <t>130233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>228627</t>
+          <t>254115</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>154526</t>
+          <t>223266</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272693</t>
+          <t>286032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>77691</t>
+          <t>88324</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61871</t>
+          <t>70888</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95995</t>
+          <t>106326</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86756</t>
+          <t>99168</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43060</t>
+          <t>82410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118867</t>
+          <t>117054</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>164447</t>
+          <t>187492</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106727</t>
+          <t>163320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196174</t>
+          <t>213859</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>795614</t>
+          <t>867639</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>795614</t>
+          <t>867639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>795614</t>
+          <t>867639</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>917496</t>
+          <t>794344</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>917496</t>
+          <t>794344</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>917496</t>
+          <t>794344</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1713111</t>
+          <t>1661983</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1713111</t>
+          <t>1661983</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1713111</t>
+          <t>1661983</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>19578</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>11871</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29433</t>
+          <t>32742</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19726</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28248</t>
+          <t>32869</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>42394</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28611</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52517</t>
+          <t>57017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>15413</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>25032</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>32688</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15387</t>
+          <t>23131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31510</t>
+          <t>44594</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>34988</t>
+          <t>48101</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25140</t>
+          <t>36219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47021</t>
+          <t>62538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103977</t>
+          <t>105722</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88562</t>
+          <t>91030</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>123226</t>
+          <t>122624</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>104785</t>
+          <t>113845</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92118</t>
+          <t>99595</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117637</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>208763</t>
+          <t>219566</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>186675</t>
+          <t>199530</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>228814</t>
+          <t>239746</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33494</t>
+          <t>34495</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>24170</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44129</t>
+          <t>46444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34122</t>
+          <t>36350</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25167</t>
+          <t>27302</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>47019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>67616</t>
+          <t>70845</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>53649</t>
+          <t>56410</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82470</t>
+          <t>87080</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25468</t>
+          <t>27171</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17035</t>
+          <t>18869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36012</t>
+          <t>38359</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>29327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43442</t>
+          <t>49335</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>59169</t>
+          <t>66236</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47260</t>
+          <t>53018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74777</t>
+          <t>81949</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>194246</t>
+          <t>202378</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>194246</t>
+          <t>202378</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>194246</t>
+          <t>202378</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>214544</t>
+          <t>244765</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>214544</t>
+          <t>244765</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>214544</t>
+          <t>244765</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>408790</t>
+          <t>447143</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>408790</t>
+          <t>447143</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>408790</t>
+          <t>447143</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>118610</t>
+          <t>113722</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91612</t>
+          <t>88877</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157423</t>
+          <t>145369</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>105088</t>
+          <t>118456</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65028</t>
+          <t>100185</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130187</t>
+          <t>140078</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>223698</t>
+          <t>232178</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169598</t>
+          <t>199427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>267427</t>
+          <t>270903</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>285861</t>
+          <t>337909</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255286</t>
+          <t>304790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>319838</t>
+          <t>375012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>587253</t>
+          <t>438247</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>435368</t>
+          <t>406546</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>913998</t>
+          <t>469069</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>873113</t>
+          <t>776157</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>711043</t>
+          <t>734137</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1341388</t>
+          <t>823741</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>475019</t>
+          <t>505249</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>440040</t>
+          <t>466915</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>514421</t>
+          <t>544725</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>421563</t>
+          <t>454358</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>262760</t>
+          <t>426533</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>500669</t>
+          <t>488187</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>896582</t>
+          <t>959607</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>650220</t>
+          <t>910296</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>985972</t>
+          <t>1006562</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>191683</t>
+          <t>211138</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>166118</t>
+          <t>185584</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>217463</t>
+          <t>239569</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>185868</t>
+          <t>205796</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>115357</t>
+          <t>182170</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>223450</t>
+          <t>229352</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>377551</t>
+          <t>416934</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>289206</t>
+          <t>381337</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>422857</t>
+          <t>453433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>136986</t>
+          <t>152423</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>116576</t>
+          <t>131188</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>160290</t>
+          <t>177318</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>169115</t>
+          <t>192161</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102225</t>
+          <t>170561</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>205035</t>
+          <t>214388</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>306101</t>
+          <t>344584</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>236532</t>
+          <t>315534</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>346208</t>
+          <t>380345</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1208159</t>
+          <t>1320441</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1208159</t>
+          <t>1320441</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1208159</t>
+          <t>1320441</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1468887</t>
+          <t>1409018</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1468887</t>
+          <t>1409018</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1468887</t>
+          <t>1409018</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2677045</t>
+          <t>2729459</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2677045</t>
+          <t>2729459</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2677045</t>
+          <t>2729459</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
